--- a/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0001T0006Z000C1N37_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0001T0006Z000C1N37_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>53.95169021047885</v>
+        <v>8.767149659202813</v>
       </c>
       <c r="D2" t="n">
-        <v>27.05993054588745</v>
+        <v>4.39723871370671</v>
       </c>
       <c r="E2" t="n">
-        <v>12.42801998091624</v>
+        <v>2.019553246898889</v>
       </c>
       <c r="F2" t="n">
-        <v>8.55255551216054</v>
+        <v>1.389790270726088</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>48.02606394973936</v>
+        <v>7.804235391832647</v>
       </c>
       <c r="D3" t="n">
-        <v>34.67788719612452</v>
+        <v>5.635156669370234</v>
       </c>
       <c r="E3" t="n">
-        <v>12.42801998091624</v>
+        <v>2.019553246898889</v>
       </c>
       <c r="F3" t="n">
-        <v>8.55255551216054</v>
+        <v>1.389790270726088</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>59.56509213345966</v>
+        <v>9.679327471687195</v>
       </c>
       <c r="D4" t="n">
-        <v>15.93893621129184</v>
+        <v>2.590077134334924</v>
       </c>
       <c r="E4" t="n">
-        <v>12.42801998091624</v>
+        <v>2.019553246898889</v>
       </c>
       <c r="F4" t="n">
-        <v>8.55255551216054</v>
+        <v>1.389790270726088</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>41.33109264655075</v>
+        <v>6.716302555064497</v>
       </c>
       <c r="D5" t="n">
-        <v>21.26711908078004</v>
+        <v>3.455906850626757</v>
       </c>
       <c r="E5" t="n">
-        <v>12.42801998091624</v>
+        <v>2.019553246898889</v>
       </c>
       <c r="F5" t="n">
-        <v>8.55255551216054</v>
+        <v>1.389790270726088</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>61.351866914963</v>
+        <v>9.969678373681489</v>
       </c>
       <c r="D6" t="n">
-        <v>3.963217752664779</v>
+        <v>0.6440228848080266</v>
       </c>
       <c r="E6" t="n">
-        <v>12.42801998091624</v>
+        <v>2.019553246898889</v>
       </c>
       <c r="F6" t="n">
-        <v>8.55255551216054</v>
+        <v>1.389790270726088</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>19.53087285748028</v>
+        <v>3.173766839340545</v>
       </c>
       <c r="D7" t="n">
-        <v>19.73099584911137</v>
+        <v>3.206286825480597</v>
       </c>
       <c r="E7" t="n">
-        <v>12.42801998091624</v>
+        <v>2.019553246898889</v>
       </c>
       <c r="F7" t="n">
-        <v>8.55255551216054</v>
+        <v>1.389790270726088</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>28.99453968048919</v>
+        <v>4.711612698079493</v>
       </c>
       <c r="D8" t="n">
-        <v>33.32792412058709</v>
+        <v>5.415787669595403</v>
       </c>
       <c r="E8" t="n">
-        <v>12.42801998091624</v>
+        <v>2.019553246898889</v>
       </c>
       <c r="F8" t="n">
-        <v>8.55255551216054</v>
+        <v>1.389790270726088</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>34.72914431145997</v>
+        <v>5.643485950612245</v>
       </c>
       <c r="D9" t="n">
-        <v>23.67698734928648</v>
+        <v>3.847510444259053</v>
       </c>
       <c r="E9" t="n">
-        <v>12.42801998091624</v>
+        <v>2.019553246898889</v>
       </c>
       <c r="F9" t="n">
-        <v>8.55255551216054</v>
+        <v>1.389790270726088</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>52.35581769960597</v>
+        <v>8.50782037618597</v>
       </c>
       <c r="D10" t="n">
-        <v>12.05428444786362</v>
+        <v>1.958821222777838</v>
       </c>
       <c r="E10" t="n">
-        <v>12.42801998091624</v>
+        <v>2.019553246898889</v>
       </c>
       <c r="F10" t="n">
-        <v>8.55255551216054</v>
+        <v>1.389790270726088</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>51.75648792707849</v>
+        <v>8.410429288150254</v>
       </c>
       <c r="D11" t="n">
-        <v>17.79768645126584</v>
+        <v>2.8921240483307</v>
       </c>
       <c r="E11" t="n">
-        <v>12.42801998091624</v>
+        <v>2.019553246898889</v>
       </c>
       <c r="F11" t="n">
-        <v>8.55255551216054</v>
+        <v>1.389790270726088</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>47.9122905531767</v>
+        <v>7.785747214891213</v>
       </c>
       <c r="D12" t="n">
-        <v>24.85323043935345</v>
+        <v>4.038649946394936</v>
       </c>
       <c r="E12" t="n">
-        <v>12.42801998091624</v>
+        <v>2.019553246898889</v>
       </c>
       <c r="F12" t="n">
-        <v>8.55255551216054</v>
+        <v>1.389790270726088</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
